--- a/files/movimientos.xlsx
+++ b/files/movimientos.xlsx
@@ -1225,11 +1225,6 @@
       <c r="J18" t="n">
         <v>2401</v>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>ENTIDAD PRESTADORA DE SERVICIOS DE SANEA</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1435,11 +1430,6 @@
       <c r="J23" t="n">
         <v>2401</v>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>CONSORCIO ELECTRICO DE VILLACURI S.A.C.</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1631,11 +1621,6 @@
           <t>Referencia Beneficiari</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>WESTERN UNION PERU S.A.</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2135,11 +2120,6 @@
       <c r="J38" t="n">
         <v>2401</v>
       </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>CAJA MUNICIPAL DE AHORRO Y CREDITO DE AR</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3129,11 +3109,6 @@
           <t>PAGO PROVEEDORES RIPLE</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>TIENDAS POR DEPARTAMENTO RIPLEY S.A.C.</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4102,11 +4077,6 @@
           <t>Pago Fact.203712041620</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>COMPANIA ELECTRICA EL PLATANAL S.A.</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4327,11 +4297,6 @@
           <t>Referencia Beneficiari</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>WESTERN UNION PERU S.A.</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4694,11 +4659,6 @@
           <t>Referencia Beneficiari</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>ON EMPRESAS S.A.C.</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5163,11 +5123,6 @@
       <c r="J105" t="n">
         <v>2401</v>
       </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>CAJA MUNICIPAL DE AHORRO Y CREDITO DE AR</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5687,11 +5642,6 @@
       <c r="J116" t="n">
         <v>2401</v>
       </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>ENTIDAD PRESTADORA DE SERVICIOS DE SANEA</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7956,11 +7906,6 @@
       <c r="J167" t="n">
         <v>2401</v>
       </c>
-      <c r="L167" t="inlineStr">
-        <is>
-          <t>VIETTEL PERU S.A.C - CAJ</t>
-        </is>
-      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -8005,11 +7950,6 @@
           <t>Pago0002301550-2026-FE</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>FENIX POWER PERU S.A.</t>
-        </is>
-      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8240,11 +8180,6 @@
           <t>Referencia Beneficiari</t>
         </is>
       </c>
-      <c r="L173" t="inlineStr">
-        <is>
-          <t>WESTERN UNION PERU S.A.</t>
-        </is>
-      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -8641,11 +8576,6 @@
           <t>Referencia Beneficiari</t>
         </is>
       </c>
-      <c r="L182" t="inlineStr">
-        <is>
-          <t>ALDEAS INFANTILES SOS PERU - ASOCIACION NACIONAL</t>
-        </is>
-      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -8685,11 +8615,6 @@
       <c r="J183" t="n">
         <v>2401</v>
       </c>
-      <c r="L183" t="inlineStr">
-        <is>
-          <t>CAJA MUNICIPAL DE AHORRO Y CREDITO DE AR</t>
-        </is>
-      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -8729,11 +8654,6 @@
       <c r="J184" t="n">
         <v>2401</v>
       </c>
-      <c r="L184" t="inlineStr">
-        <is>
-          <t>REPRESENT.Y SERVICIOS - INGENIEROS SRL</t>
-        </is>
-      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -9150,11 +9070,6 @@
       <c r="J193" t="n">
         <v>2401</v>
       </c>
-      <c r="L193" t="inlineStr">
-        <is>
-          <t>REPRESENT.Y SERVICIOS - INGENIEROS SRL</t>
-        </is>
-      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -10686,11 +10601,6 @@
       <c r="J227" t="n">
         <v>2401</v>
       </c>
-      <c r="L227" t="inlineStr">
-        <is>
-          <t>EGEMSA</t>
-        </is>
-      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -11682,11 +11592,6 @@
           <t>Referencia Beneficiari</t>
         </is>
       </c>
-      <c r="L251" t="inlineStr">
-        <is>
-          <t>WESTERN UNION PERU S.A.</t>
-        </is>
-      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -12235,11 +12140,6 @@
       <c r="J263" t="n">
         <v>2401</v>
       </c>
-      <c r="L263" t="inlineStr">
-        <is>
-          <t>CAJA MUNICIPAL DE AHORRO Y CREDITO DE AR</t>
-        </is>
-      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -12685,11 +12585,6 @@
       <c r="J273" t="n">
         <v>2401</v>
       </c>
-      <c r="L273" t="inlineStr">
-        <is>
-          <t>DIAR INGENIEROS S.A.</t>
-        </is>
-      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -13429,11 +13324,6 @@
       <c r="J289" t="n">
         <v>2401</v>
       </c>
-      <c r="L289" t="inlineStr">
-        <is>
-          <t>EMPRESA DE GENERACION ELECTRICA DE AREQUIPA S.A.</t>
-        </is>
-      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -16397,11 +16287,6 @@
           <t>0000010041</t>
         </is>
       </c>
-      <c r="L361" t="inlineStr">
-        <is>
-          <t>KONDU S.A.C</t>
-        </is>
-      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -16446,11 +16331,6 @@
           <t>Referencia Beneficiari</t>
         </is>
       </c>
-      <c r="L362" t="inlineStr">
-        <is>
-          <t>FIDEICOMISO ELECTROPERU</t>
-        </is>
-      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -16495,11 +16375,6 @@
           <t>0000010041</t>
         </is>
       </c>
-      <c r="L363" t="inlineStr">
-        <is>
-          <t>KALLPA GENERACION SA</t>
-        </is>
-      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -16539,11 +16414,6 @@
       <c r="J364" t="n">
         <v>2401</v>
       </c>
-      <c r="L364" t="inlineStr">
-        <is>
-          <t>ENTIDAD PRESTADORA DE SERVICIOS DE SANEA</t>
-        </is>
-      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -16622,11 +16492,6 @@
       <c r="J366" t="n">
         <v>2401</v>
       </c>
-      <c r="L366" t="inlineStr">
-        <is>
-          <t>COFIDE FID FISE</t>
-        </is>
-      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -16852,11 +16717,6 @@
           <t>0000010041</t>
         </is>
       </c>
-      <c r="L371" t="inlineStr">
-        <is>
-          <t>ORAZUL ENERGY PERU SA</t>
-        </is>
-      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -16999,11 +16859,6 @@
           <t>Referencia Beneficiari</t>
         </is>
       </c>
-      <c r="L374" t="inlineStr">
-        <is>
-          <t>WESTERN UNION PERU S.A.</t>
-        </is>
-      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -17527,11 +17382,6 @@
       <c r="J386" t="n">
         <v>2401</v>
       </c>
-      <c r="L386" t="inlineStr">
-        <is>
-          <t>ENTIDAD PRESTADORA DE SERVICIOS DE SANEA</t>
-        </is>
-      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -17571,11 +17421,6 @@
       <c r="J387" t="n">
         <v>2401</v>
       </c>
-      <c r="L387" t="inlineStr">
-        <is>
-          <t>ENTIDAD PRESTADORA DE SERVICIOS DE SANEA</t>
-        </is>
-      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -18618,11 +18463,6 @@
       <c r="J410" t="n">
         <v>2401</v>
       </c>
-      <c r="L410" t="inlineStr">
-        <is>
-          <t>CAJA MUNICIPAL DE AHORRO Y CREDITO DE AR</t>
-        </is>
-      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -18706,11 +18546,6 @@
       <c r="J412" t="n">
         <v>2401</v>
       </c>
-      <c r="L412" t="inlineStr">
-        <is>
-          <t>ENTIDAD PRESTADORA DE SERVICIOS DE SANEA</t>
-        </is>
-      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -23347,11 +23182,6 @@
           <t>Ref 20103117560-01-F06</t>
         </is>
       </c>
-      <c r="L516" t="inlineStr">
-        <is>
-          <t>VARI ENERGIA SAC</t>
-        </is>
-      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -24563,11 +24393,6 @@
           <t>S017603022026</t>
         </is>
       </c>
-      <c r="L545" t="inlineStr">
-        <is>
-          <t>LUZ DEL SUR S.A.A.</t>
-        </is>
-      </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -24793,11 +24618,6 @@
           <t>Referencia Beneficiari</t>
         </is>
       </c>
-      <c r="L550" t="inlineStr">
-        <is>
-          <t>WESTERN UNION PERU S.A.</t>
-        </is>
-      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -25321,11 +25141,6 @@
       <c r="J562" t="n">
         <v>2401</v>
       </c>
-      <c r="L562" t="inlineStr">
-        <is>
-          <t>CAJA MUNICIPAL DE AHORRO Y CREDITO DE AR</t>
-        </is>
-      </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -25522,11 +25337,6 @@
       <c r="J566" t="n">
         <v>2401</v>
       </c>
-      <c r="L566" t="inlineStr">
-        <is>
-          <t>VIETTEL PERU S.A.C - CAJ</t>
-        </is>
-      </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -25713,11 +25523,6 @@
       <c r="J570" t="n">
         <v>2401</v>
       </c>
-      <c r="L570" t="inlineStr">
-        <is>
-          <t>VIETTEL PERU S.A.C - CAJ</t>
-        </is>
-      </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -25948,11 +25753,6 @@
       <c r="J575" t="n">
         <v>2401</v>
       </c>
-      <c r="L575" t="inlineStr">
-        <is>
-          <t>TERMOSELVA S.R.L.</t>
-        </is>
-      </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -25997,11 +25797,6 @@
           <t>S018104022026</t>
         </is>
       </c>
-      <c r="L576" t="inlineStr">
-        <is>
-          <t>INLAND ENERGY SAC</t>
-        </is>
-      </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -26046,11 +25841,6 @@
           <t>01-F061-00020521</t>
         </is>
       </c>
-      <c r="L577" t="inlineStr">
-        <is>
-          <t>INVERSIONES SHAQSHA S.A.C.</t>
-        </is>
-      </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -27145,11 +26935,6 @@
           <t>01-F061-00020467</t>
         </is>
       </c>
-      <c r="L603" t="inlineStr">
-        <is>
-          <t>STATKRAFT PERU SA</t>
-        </is>
-      </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
@@ -27370,11 +27155,6 @@
           <t>Referencia Beneficiari</t>
         </is>
       </c>
-      <c r="L608" t="inlineStr">
-        <is>
-          <t>WESTERN UNION PERU S.A.</t>
-        </is>
-      </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
@@ -27463,11 +27243,6 @@
           <t>Pago beneficiario</t>
         </is>
       </c>
-      <c r="L610" t="inlineStr">
-        <is>
-          <t>ELECTRO DUNAS S.A.A.</t>
-        </is>
-      </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
@@ -28021,11 +27796,6 @@
       <c r="J622" t="n">
         <v>2401</v>
       </c>
-      <c r="L622" t="inlineStr">
-        <is>
-          <t>CAJA MUNICIPAL DE AHORRO Y CREDITO DE AR</t>
-        </is>
-      </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
@@ -28692,11 +28462,6 @@
           <t>Pago Fact.20494</t>
         </is>
       </c>
-      <c r="L636" t="inlineStr">
-        <is>
-          <t>TERMOCHILCA S.A.C.</t>
-        </is>
-      </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
@@ -28785,11 +28550,6 @@
           <t>Pago Fact.20485</t>
         </is>
       </c>
-      <c r="L638" t="inlineStr">
-        <is>
-          <t>COMPANIA ELECTRICA EL PLATANAL S.A.</t>
-        </is>
-      </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
@@ -28834,11 +28594,6 @@
           <t>Pago Fact.20505</t>
         </is>
       </c>
-      <c r="L639" t="inlineStr">
-        <is>
-          <t>CELEPSA RENOVABLES SRL</t>
-        </is>
-      </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -29831,11 +29586,6 @@
           <t>Referencia Beneficiari</t>
         </is>
       </c>
-      <c r="L662" t="inlineStr">
-        <is>
-          <t>WESTERN UNION PERU S.A.</t>
-        </is>
-      </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
@@ -30301,11 +30051,6 @@
       <c r="J672" t="n">
         <v>2401</v>
       </c>
-      <c r="L672" t="inlineStr">
-        <is>
-          <t>CAJA MUNICIPAL DE AHORRO Y CREDITO DE AR</t>
-        </is>
-      </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
@@ -32170,11 +31915,6 @@
           <t>Pago0002300998-2026-FE</t>
         </is>
       </c>
-      <c r="L713" t="inlineStr">
-        <is>
-          <t>FENIX POWER PERU S.A.</t>
-        </is>
-      </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
@@ -32400,11 +32140,6 @@
       <c r="J718" t="n">
         <v>2401</v>
       </c>
-      <c r="L718" t="inlineStr">
-        <is>
-          <t>EMPRESA DE GENERACION ELECTRICA SAN GABAN S.A.</t>
-        </is>
-      </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
@@ -33382,11 +33117,6 @@
           <t>Referencia Beneficiari</t>
         </is>
       </c>
-      <c r="L741" t="inlineStr">
-        <is>
-          <t>WESTERN UNION PERU S.A.</t>
-        </is>
-      </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
@@ -34962,11 +34692,6 @@
       <c r="J776" t="n">
         <v>2401</v>
       </c>
-      <c r="L776" t="inlineStr">
-        <is>
-          <t>CAJA MUNICIPAL DE AHORRO Y CREDITO DE AR</t>
-        </is>
-      </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
@@ -35848,11 +35573,6 @@
           <t>PAGO DE PROVEEDORES</t>
         </is>
       </c>
-      <c r="L795" t="inlineStr">
-        <is>
-          <t>FIDEICOMISO ELECTROPERU</t>
-        </is>
-      </c>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
@@ -36215,11 +35935,6 @@
       <c r="J803" t="n">
         <v>2401</v>
       </c>
-      <c r="L803" t="inlineStr">
-        <is>
-          <t>HYDRO GLOBAL PERU S.A.C.</t>
-        </is>
-      </c>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
@@ -36262,11 +35977,6 @@
       <c r="K804" t="inlineStr">
         <is>
           <t>Pago beneficiario</t>
-        </is>
-      </c>
-      <c r="L804" t="inlineStr">
-        <is>
-          <t>SINDICATO ENERGETICO S.A.</t>
         </is>
       </c>
     </row>
